--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67635_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67635_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R29e58559a0514af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd805cf99c2e14abc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.3263</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.6150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.7843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.8637</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.1265</x:v>
+        <x:v>     17.7843</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67635_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67635_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd805cf99c2e14abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb453ff0f164c41f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,711 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5937</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0407</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0407</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.8862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9518</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.7843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.0411</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.8495</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.5204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.7843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.4469</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.0293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.2866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.9106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.2152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.8862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.5204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.5204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.8442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.1142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.8262</x:v>
+        <x:v>     16.4629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.8262</x:v>
+        <x:v>     16.7862</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.3450</x:v>
+        <x:v>     16.7862</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.8262</x:v>
+        <x:v>     17.1142</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.3263</x:v>
+        <x:v>     17.4469</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.8637</x:v>
+        <x:v>     18.2994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.0018</x:v>
+        <x:v>     27.1832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.5524</x:v>
+        <x:v>     26.4934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.4577</x:v>
+        <x:v>     26.0407</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.0018</x:v>
+        <x:v>     26.0407</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9518</x:v>
+        <x:v>     26.4934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,22 +1869,22 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     26.4934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     28.3623</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.8262</x:v>
       </x:c>
     </x:row>
     <x:row>
